--- a/Data/EXCEL/Transfer/salemon/20240711/6547-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/6547-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FCE259CB-BAE8-48D0-BA5E-09EB2961F28F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F02DEEFC-FAB9-4F97-A1DF-15461C467ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{5DE2BA6D-2C5C-46EE-9267-EB4C4545AA14}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{43785ED4-A908-4A98-8EB6-ED6F513B89E5}"/>
   </bookViews>
   <sheets>
     <sheet name="6547-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,24 +1261,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{851F9E18-73DC-43C5-9E81-EDA35FF65395}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{252961E7-4F8C-43C5-96FB-CCC52AEBA875}">
   <dimension ref="A1:Q229"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1305,7 +1305,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1387,7 +1387,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1426,7 +1426,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>45413</v>
       </c>
@@ -1532,7 +1532,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>45352</v>
       </c>
@@ -1638,7 +1638,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1691,7 +1691,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>45292</v>
       </c>
@@ -1744,7 +1744,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>45231</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1903,7 +1903,7 @@
         <v>-13.5</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>45170</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>-36</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>-70.099999999999994</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>45108</v>
       </c>
@@ -2062,7 +2062,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>45047</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>44986</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2327,7 +2327,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>44927</v>
       </c>
@@ -2380,7 +2380,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2433,7 +2433,7 @@
         <v>-88.9</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>44866</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>-88</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2539,7 +2539,7 @@
         <v>-80.900000000000006</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>44805</v>
       </c>
@@ -2592,7 +2592,7 @@
         <v>-72.7</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2645,7 +2645,7 @@
         <v>-53.5</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>44743</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>7395.2</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>8222.2999999999993</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>44682</v>
       </c>
@@ -2804,7 +2804,7 @@
         <v>10634.4</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2857,7 +2857,7 @@
         <v>10560.6</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>44621</v>
       </c>
@@ -2910,7 +2910,7 @@
         <v>10292.4</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>11840.8</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>44562</v>
       </c>
@@ -3016,7 +3016,7 @@
         <v>11689.2</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>28415.5</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>44501</v>
       </c>
@@ -3122,7 +3122,7 @@
         <v>36631.800000000003</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3175,7 +3175,7 @@
         <v>30955.599999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>44440</v>
       </c>
@@ -3228,7 +3228,7 @@
         <v>27213.8</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3281,7 +3281,7 @@
         <v>25731.9</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>44378</v>
       </c>
@@ -3334,7 +3334,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3387,7 +3387,7 @@
         <v>149.9</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>44317</v>
       </c>
@@ -3440,7 +3440,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>44287</v>
       </c>
@@ -3493,7 +3493,7 @@
         <v>554.79999999999995</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>44256</v>
       </c>
@@ -3546,7 +3546,7 @@
         <v>554.79999999999995</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44228</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>316.7</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>44197</v>
       </c>
@@ -3652,7 +3652,7 @@
         <v>316.7</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>44166</v>
       </c>
@@ -3705,7 +3705,7 @@
         <v>927.3</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>44136</v>
       </c>
@@ -3758,7 +3758,7 @@
         <v>627.9</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>44105</v>
       </c>
@@ -3811,7 +3811,7 @@
         <v>428.3</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>44075</v>
       </c>
@@ -3864,7 +3864,7 @@
         <v>615.6</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>44044</v>
       </c>
@@ -3917,7 +3917,7 @@
         <v>342.8</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>44013</v>
       </c>
@@ -3970,7 +3970,7 @@
         <v>254.1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>43983</v>
       </c>
@@ -4023,7 +4023,7 @@
         <v>154.80000000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
         <v>43952</v>
       </c>
@@ -4076,7 +4076,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>43922</v>
       </c>
@@ -4129,7 +4129,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="10">
         <v>43891</v>
       </c>
@@ -4182,7 +4182,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>43862</v>
       </c>
@@ -4235,7 +4235,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="10">
         <v>43831</v>
       </c>
@@ -4288,7 +4288,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>43800</v>
       </c>
@@ -4341,7 +4341,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="10">
         <v>43770</v>
       </c>
@@ -4394,7 +4394,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>43739</v>
       </c>
@@ -4447,7 +4447,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="10">
         <v>43709</v>
       </c>
@@ -4500,7 +4500,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>43678</v>
       </c>
@@ -4553,7 +4553,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="10">
         <v>43647</v>
       </c>
@@ -4606,7 +4606,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>43617</v>
       </c>
@@ -4659,7 +4659,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="10">
         <v>43586</v>
       </c>
@@ -4712,7 +4712,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>43556</v>
       </c>
@@ -4765,7 +4765,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="10">
         <v>43525</v>
       </c>
@@ -4818,7 +4818,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>43497</v>
       </c>
@@ -4871,7 +4871,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="10">
         <v>43466</v>
       </c>
@@ -4924,7 +4924,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>43435</v>
       </c>
@@ -4977,7 +4977,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="10">
         <v>43405</v>
       </c>
@@ -5030,7 +5030,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>43374</v>
       </c>
@@ -5083,7 +5083,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="10">
         <v>43344</v>
       </c>
@@ -5136,7 +5136,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>43313</v>
       </c>
@@ -5189,7 +5189,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="10">
         <v>43282</v>
       </c>
@@ -5242,7 +5242,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>43252</v>
       </c>
@@ -5295,7 +5295,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="10">
         <v>43221</v>
       </c>
@@ -5348,7 +5348,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>43191</v>
       </c>
@@ -5401,7 +5401,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="10">
         <v>43160</v>
       </c>
@@ -5454,7 +5454,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>43132</v>
       </c>
@@ -5507,7 +5507,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="10">
         <v>43101</v>
       </c>
@@ -5560,7 +5560,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>43070</v>
       </c>
@@ -5613,7 +5613,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="10">
         <v>43040</v>
       </c>
@@ -5666,7 +5666,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>43009</v>
       </c>
@@ -5719,7 +5719,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="10">
         <v>42979</v>
       </c>
@@ -5772,7 +5772,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>42948</v>
       </c>
@@ -5825,7 +5825,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="10">
         <v>42917</v>
       </c>
@@ -5878,7 +5878,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>42887</v>
       </c>
@@ -5931,7 +5931,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="10">
         <v>42856</v>
       </c>
@@ -5984,7 +5984,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>42826</v>
       </c>
@@ -6037,7 +6037,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="10">
         <v>42795</v>
       </c>
@@ -6090,7 +6090,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>42767</v>
       </c>
@@ -6143,7 +6143,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="10">
         <v>42736</v>
       </c>
@@ -6196,7 +6196,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>42705</v>
       </c>
@@ -6249,7 +6249,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="10">
         <v>42675</v>
       </c>
@@ -6302,7 +6302,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
         <v>42644</v>
       </c>
@@ -6355,7 +6355,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" s="10">
         <v>42614</v>
       </c>
@@ -6408,7 +6408,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" s="5">
         <v>42583</v>
       </c>
@@ -6461,7 +6461,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" s="10">
         <v>42552</v>
       </c>
@@ -6514,7 +6514,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
         <v>42522</v>
       </c>
@@ -6567,7 +6567,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" s="10">
         <v>42491</v>
       </c>
@@ -6620,7 +6620,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" s="5">
         <v>42461</v>
       </c>
@@ -6673,7 +6673,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" s="10">
         <v>42430</v>
       </c>
@@ -6726,7 +6726,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" s="5">
         <v>42401</v>
       </c>
@@ -6779,7 +6779,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" s="10">
         <v>42370</v>
       </c>
@@ -6832,7 +6832,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" s="5">
         <v>42339</v>
       </c>
@@ -6885,7 +6885,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" s="10">
         <v>42309</v>
       </c>
@@ -6938,7 +6938,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" s="5">
         <v>42278</v>
       </c>
@@ -6991,7 +6991,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" s="10">
         <v>42248</v>
       </c>
@@ -7044,7 +7044,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" s="5">
         <v>42217</v>
       </c>
@@ -7097,7 +7097,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" s="10">
         <v>42186</v>
       </c>
@@ -7150,7 +7150,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
         <v>42156</v>
       </c>
@@ -7203,582 +7203,582 @@
         <v>17</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" s="10">
         <v>45413</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" s="10">
         <v>45352</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" s="10">
         <v>45292</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" s="10">
         <v>45231</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" s="10">
         <v>45170</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" s="10">
         <v>45108</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" s="10">
         <v>45047</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" s="10">
         <v>44986</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" s="10">
         <v>44927</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" s="10">
         <v>44866</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A137" s="10">
         <v>44805</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A138" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A139" s="10">
         <v>44743</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A140" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A141" s="10">
         <v>44682</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A142" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A143" s="10">
         <v>44621</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A144" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" s="10">
         <v>44562</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A146" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A147" s="10">
         <v>44501</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A148" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A149" s="10">
         <v>44440</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A150" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A151" s="10">
         <v>44378</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A153" s="5">
         <v>44348</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A154" s="10">
         <v>44317</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A155" s="5">
         <v>44287</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A156" s="10">
         <v>44256</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A157" s="5">
         <v>44228</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A158" s="10">
         <v>44197</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A159" s="5">
         <v>44166</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A160" s="10">
         <v>44136</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A161" s="5">
         <v>44105</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A162" s="10">
         <v>44075</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A163" s="5">
         <v>44044</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A164" s="10">
         <v>44013</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A165" s="5">
         <v>43983</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A166" s="10">
         <v>43952</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A167" s="5">
         <v>43922</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A168" s="10">
         <v>43891</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A169" s="5">
         <v>43862</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A170" s="10">
         <v>43831</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A172" s="5">
         <v>43800</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A173" s="10">
         <v>43770</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A174" s="5">
         <v>43739</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A175" s="10">
         <v>43709</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A176" s="5">
         <v>43678</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A177" s="10">
         <v>43647</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A178" s="5">
         <v>43617</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A179" s="10">
         <v>43586</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A180" s="5">
         <v>43556</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A181" s="10">
         <v>43525</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A182" s="5">
         <v>43497</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A183" s="10">
         <v>43466</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A184" s="5">
         <v>43435</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A185" s="10">
         <v>43405</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A186" s="5">
         <v>43374</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A187" s="10">
         <v>43344</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A188" s="5">
         <v>43313</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A189" s="10">
         <v>43282</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A191" s="5">
         <v>43252</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A192" s="10">
         <v>43221</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A193" s="5">
         <v>43191</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A194" s="10">
         <v>43160</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A195" s="5">
         <v>43132</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A196" s="10">
         <v>43101</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A197" s="5">
         <v>43070</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A198" s="10">
         <v>43040</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A199" s="5">
         <v>43009</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A200" s="10">
         <v>42979</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A201" s="5">
         <v>42948</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A202" s="10">
         <v>42917</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A203" s="5">
         <v>42887</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A204" s="10">
         <v>42856</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A205" s="5">
         <v>42826</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A206" s="10">
         <v>42795</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A207" s="5">
         <v>42767</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A208" s="10">
         <v>42736</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A210" s="5">
         <v>42705</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A211" s="10">
         <v>42675</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A212" s="5">
         <v>42644</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A213" s="10">
         <v>42614</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A214" s="5">
         <v>42583</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A215" s="10">
         <v>42552</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A216" s="5">
         <v>42522</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A217" s="10">
         <v>42491</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A218" s="5">
         <v>42461</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A219" s="10">
         <v>42430</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A220" s="5">
         <v>42401</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A221" s="10">
         <v>42370</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A222" s="5">
         <v>42339</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A223" s="10">
         <v>42309</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A224" s="5">
         <v>42278</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A225" s="10">
         <v>42248</v>
       </c>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A226" s="5">
         <v>42217</v>
       </c>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A227" s="10">
         <v>42186</v>
       </c>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A229" s="5">
         <v>42156</v>
       </c>
